--- a/testing-column.xlsx
+++ b/testing-column.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\leading-zeros-dates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C737DB4-AD57-4A5F-A1BF-CF6AE55D7201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912A5CC4-6151-4168-A3CB-9887192B9DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25770" yWindow="150" windowWidth="25785" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="186">
   <si>
     <t>Solved</t>
   </si>
@@ -557,6 +557,27 @@
   </si>
   <si>
     <t>12/12/1992</t>
+  </si>
+  <si>
+    <t>January 30, 2015 - June 15, 2015</t>
+  </si>
+  <si>
+    <t>01/30/2015 - 06/15/2015</t>
+  </si>
+  <si>
+    <t>1966-67;1970-1973, 1976-77</t>
+  </si>
+  <si>
+    <t>01/01/1966 - 12/31/1967</t>
+  </si>
+  <si>
+    <t>July 1, 2015 – June 30, 2016</t>
+  </si>
+  <si>
+    <t>07/01/2015 - 06/30/2016</t>
+  </si>
+  <si>
+    <t>01/01/2016 - 12/31/2016</t>
   </si>
 </sst>
 </file>
@@ -566,7 +587,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,6 +599,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -615,12 +641,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -923,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -955,45 +987,49 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
+      <c r="A2" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
+      <c r="A3" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
+        <v>180</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1001,16 +1037,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1018,16 +1051,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1035,13 +1065,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1049,13 +1079,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1063,13 +1096,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1077,16 +1113,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1094,16 +1127,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1111,16 +1141,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>6</v>
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1128,13 +1155,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
@@ -1145,13 +1172,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
@@ -1162,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
@@ -1176,16 +1203,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
@@ -1196,13 +1223,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
@@ -1213,13 +1240,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
@@ -1227,16 +1254,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1244,27 +1274,30 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>34</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
         <v>6</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
         <v>15</v>
@@ -1272,86 +1305,92 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22">
-        <v>40178</v>
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>185</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="2">
-        <v>36161</v>
-      </c>
-      <c r="C23" t="s">
-        <v>43</v>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="2">
-        <v>36557</v>
-      </c>
-      <c r="C24" t="s">
-        <v>44</v>
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
-      <c r="B25" t="s">
-        <v>45</v>
+      <c r="B25">
+        <v>40178</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
-      <c r="B26" t="s">
-        <v>47</v>
+      <c r="B26" s="2">
+        <v>36161</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
-      <c r="B27" t="s">
-        <v>49</v>
+      <c r="B27" s="2">
+        <v>36557</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1359,13 +1398,13 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1373,13 +1412,13 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1387,13 +1426,13 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1401,13 +1440,13 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1415,13 +1454,13 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1429,13 +1468,13 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1443,13 +1482,13 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1457,13 +1496,13 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1471,19 +1510,13 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E36" t="s">
-        <v>64</v>
-      </c>
-      <c r="F36" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1491,19 +1524,13 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1511,19 +1538,13 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C38" t="s">
-        <v>67</v>
-      </c>
-      <c r="D38" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
-      </c>
-      <c r="F38" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1531,16 +1552,16 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D39" t="s">
         <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F39" t="s">
         <v>15</v>
@@ -1551,16 +1572,16 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D40" t="s">
         <v>6</v>
       </c>
       <c r="E40" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F40" t="s">
         <v>15</v>
@@ -1571,16 +1592,16 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D41" t="s">
         <v>6</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
@@ -1591,16 +1612,16 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
         <v>6</v>
       </c>
       <c r="E42" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
@@ -1611,16 +1632,16 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C43" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D43" t="s">
         <v>6</v>
       </c>
       <c r="E43" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
@@ -1631,16 +1652,16 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D44" t="s">
         <v>6</v>
       </c>
       <c r="E44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F44" t="s">
         <v>15</v>
@@ -1651,16 +1672,16 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D45" t="s">
         <v>6</v>
       </c>
       <c r="E45" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
@@ -1671,16 +1692,16 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D46" t="s">
         <v>6</v>
       </c>
       <c r="E46" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
@@ -1691,16 +1712,16 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D47" t="s">
         <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F47" t="s">
         <v>15</v>
@@ -1711,16 +1732,16 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D48" t="s">
         <v>6</v>
       </c>
       <c r="E48" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F48" t="s">
         <v>15</v>
@@ -1731,16 +1752,16 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C49" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D49" t="s">
         <v>6</v>
       </c>
       <c r="E49" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F49" t="s">
         <v>15</v>
@@ -1751,7 +1772,7 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C50" t="s">
         <v>80</v>
@@ -1771,7 +1792,7 @@
         <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C51" t="s">
         <v>83</v>
@@ -1791,16 +1812,16 @@
         <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C52" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D52" t="s">
         <v>6</v>
       </c>
       <c r="E52" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F52" t="s">
         <v>15</v>
@@ -1811,16 +1832,16 @@
         <v>6</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D53" t="s">
         <v>6</v>
       </c>
       <c r="E53" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F53" t="s">
         <v>15</v>
@@ -1831,13 +1852,19 @@
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C54" t="s">
-        <v>91</v>
+        <v>83</v>
+      </c>
+      <c r="D54" t="s">
+        <v>6</v>
       </c>
       <c r="E54" t="s">
-        <v>91</v>
+        <v>83</v>
+      </c>
+      <c r="F54" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1845,13 +1872,19 @@
         <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C55" t="s">
-        <v>93</v>
+        <v>87</v>
+      </c>
+      <c r="D55" t="s">
+        <v>6</v>
       </c>
       <c r="E55" t="s">
-        <v>93</v>
+        <v>87</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1859,13 +1892,19 @@
         <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>95</v>
+        <v>89</v>
+      </c>
+      <c r="D56" t="s">
+        <v>6</v>
       </c>
       <c r="E56" t="s">
-        <v>95</v>
+        <v>89</v>
+      </c>
+      <c r="F56" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1873,13 +1912,13 @@
         <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C57" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="E57" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1887,13 +1926,13 @@
         <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C58" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1901,115 +1940,97 @@
         <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="E59" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>6</v>
       </c>
-      <c r="B60" s="2">
-        <v>3272</v>
+      <c r="B60" t="s">
+        <v>96</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="E60" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="2">
-        <v>40919</v>
+      <c r="B61" t="s">
+        <v>97</v>
       </c>
       <c r="C61" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E61" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>6</v>
       </c>
-      <c r="B62" s="2">
-        <v>40960</v>
+      <c r="B62" t="s">
+        <v>98</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="E62" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>6</v>
       </c>
-      <c r="B63" t="s">
-        <v>102</v>
+      <c r="B63" s="2">
+        <v>3272</v>
       </c>
       <c r="C63" t="s">
-        <v>102</v>
-      </c>
-      <c r="D63" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="E63" t="s">
-        <v>102</v>
-      </c>
-      <c r="F63" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>6</v>
       </c>
-      <c r="B64" t="s">
-        <v>103</v>
+      <c r="B64" s="2">
+        <v>40919</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
-      </c>
-      <c r="D64" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E64" t="s">
-        <v>104</v>
-      </c>
-      <c r="F64" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>6</v>
       </c>
-      <c r="B65" t="s">
-        <v>105</v>
+      <c r="B65" s="2">
+        <v>40960</v>
       </c>
       <c r="C65" t="s">
-        <v>106</v>
-      </c>
-      <c r="D65" t="s">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="E65" t="s">
-        <v>106</v>
-      </c>
-      <c r="F65" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2017,16 +2038,16 @@
         <v>6</v>
       </c>
       <c r="B66" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C66" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D66" t="s">
         <v>6</v>
       </c>
       <c r="E66" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F66" t="s">
         <v>15</v>
@@ -2037,16 +2058,16 @@
         <v>6</v>
       </c>
       <c r="B67" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C67" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D67" t="s">
         <v>6</v>
       </c>
       <c r="E67" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F67" t="s">
         <v>15</v>
@@ -2057,16 +2078,16 @@
         <v>6</v>
       </c>
       <c r="B68" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D68" t="s">
         <v>6</v>
       </c>
       <c r="E68" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F68" t="s">
         <v>15</v>
@@ -2077,16 +2098,16 @@
         <v>6</v>
       </c>
       <c r="B69" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C69" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D69" t="s">
         <v>6</v>
       </c>
       <c r="E69" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F69" t="s">
         <v>15</v>
@@ -2096,14 +2117,20 @@
       <c r="A70" t="s">
         <v>6</v>
       </c>
-      <c r="B70">
-        <v>1900</v>
+      <c r="B70" t="s">
+        <v>109</v>
       </c>
       <c r="C70" t="s">
-        <v>115</v>
+        <v>110</v>
+      </c>
+      <c r="D70" t="s">
+        <v>6</v>
       </c>
       <c r="E70" t="s">
-        <v>115</v>
+        <v>110</v>
+      </c>
+      <c r="F70" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2111,13 +2138,19 @@
         <v>6</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C71" t="s">
-        <v>117</v>
+        <v>112</v>
+      </c>
+      <c r="D71" t="s">
+        <v>6</v>
       </c>
       <c r="E71" t="s">
-        <v>117</v>
+        <v>112</v>
+      </c>
+      <c r="F71" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2125,13 +2158,19 @@
         <v>6</v>
       </c>
       <c r="B72" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C72" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="D72" t="s">
+        <v>6</v>
       </c>
       <c r="E72" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="F72" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,13 +2178,13 @@
         <v>6</v>
       </c>
       <c r="B73">
-        <v>1980</v>
+        <v>1900</v>
       </c>
       <c r="C73" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E73" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2153,13 +2192,13 @@
         <v>6</v>
       </c>
       <c r="B74" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C74" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E74" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2167,27 +2206,27 @@
         <v>6</v>
       </c>
       <c r="B75" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C75" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E75" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>6</v>
       </c>
-      <c r="B76" t="s">
-        <v>124</v>
+      <c r="B76">
+        <v>1980</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E76" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2195,13 +2234,13 @@
         <v>6</v>
       </c>
       <c r="B77" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E77" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2209,13 +2248,13 @@
         <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C78" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="E78" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2223,7 +2262,7 @@
         <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C79" t="s">
         <v>125</v>
@@ -2237,13 +2276,13 @@
         <v>6</v>
       </c>
       <c r="B80" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C80" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="E80" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2251,13 +2290,13 @@
         <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C81" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="E81" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2265,13 +2304,13 @@
         <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C82" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E82" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2279,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="B83" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C83" t="s">
         <v>56</v>
@@ -2293,13 +2332,13 @@
         <v>6</v>
       </c>
       <c r="B84" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C84" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="E84" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2307,13 +2346,13 @@
         <v>6</v>
       </c>
       <c r="B85" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C85" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E85" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2321,13 +2360,13 @@
         <v>6</v>
       </c>
       <c r="B86" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C86" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="E86" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2335,13 +2374,13 @@
         <v>6</v>
       </c>
       <c r="B87" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C87" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="E87" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2349,24 +2388,27 @@
         <v>6</v>
       </c>
       <c r="B88" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C88" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E88" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>6</v>
       </c>
+      <c r="B89" t="s">
+        <v>139</v>
+      </c>
       <c r="C89" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2374,13 +2416,13 @@
         <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C90" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="E90" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2388,27 +2430,24 @@
         <v>6</v>
       </c>
       <c r="B91" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C91" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E91" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>6</v>
       </c>
-      <c r="B92" t="s">
-        <v>144</v>
-      </c>
       <c r="C92" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="E92" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2416,7 +2455,7 @@
         <v>6</v>
       </c>
       <c r="B93" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C93" t="s">
         <v>100</v>
@@ -2430,7 +2469,7 @@
         <v>6</v>
       </c>
       <c r="B94" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C94" t="s">
         <v>101</v>
@@ -2444,13 +2483,13 @@
         <v>6</v>
       </c>
       <c r="B95" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2458,7 +2497,7 @@
         <v>6</v>
       </c>
       <c r="B96" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C96" t="s">
         <v>100</v>
@@ -2472,13 +2511,13 @@
         <v>6</v>
       </c>
       <c r="B97" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E97" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2486,7 +2525,7 @@
         <v>6</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C98" t="s">
         <v>101</v>
@@ -2500,13 +2539,13 @@
         <v>6</v>
       </c>
       <c r="B99" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C99" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="E99" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2514,13 +2553,13 @@
         <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C100" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="E100" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -2528,13 +2567,13 @@
         <v>6</v>
       </c>
       <c r="B101" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C101" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="E101" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2542,13 +2581,13 @@
         <v>6</v>
       </c>
       <c r="B102" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C102" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="E102" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -2556,13 +2595,13 @@
         <v>6</v>
       </c>
       <c r="B103" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C103" t="s">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="E103" t="s">
-        <v>158</v>
+        <v>56</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2570,13 +2609,13 @@
         <v>6</v>
       </c>
       <c r="B104" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C104" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E104" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2584,13 +2623,13 @@
         <v>6</v>
       </c>
       <c r="B105" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C105" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E105" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2598,13 +2637,13 @@
         <v>6</v>
       </c>
       <c r="B106" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C106" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E106" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2612,13 +2651,13 @@
         <v>6</v>
       </c>
       <c r="B107" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C107" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E107" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2626,13 +2665,13 @@
         <v>6</v>
       </c>
       <c r="B108" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C108" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E108" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -2640,13 +2679,13 @@
         <v>6</v>
       </c>
       <c r="B109" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C109" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E109" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -2654,13 +2693,13 @@
         <v>6</v>
       </c>
       <c r="B110" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C110" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E110" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -2668,13 +2707,13 @@
         <v>6</v>
       </c>
       <c r="B111" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C111" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E111" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -2682,13 +2721,13 @@
         <v>6</v>
       </c>
       <c r="B112" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C112" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E112" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2696,44 +2735,87 @@
         <v>6</v>
       </c>
       <c r="B113" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C113" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E113" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>6</v>
       </c>
-      <c r="B114" s="2">
-        <v>31717</v>
+      <c r="B114" t="s">
+        <v>173</v>
       </c>
       <c r="C114" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E114" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" t="s">
+        <v>175</v>
+      </c>
+      <c r="C115" t="s">
+        <v>168</v>
+      </c>
+      <c r="E115" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>6</v>
+      </c>
+      <c r="B116" t="s">
+        <v>176</v>
+      </c>
+      <c r="C116" t="s">
+        <v>170</v>
+      </c>
+      <c r="E116" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>6</v>
+      </c>
+      <c r="B117" s="2">
+        <v>31717</v>
+      </c>
+      <c r="C117" t="s">
+        <v>177</v>
+      </c>
+      <c r="E117" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>6</v>
+      </c>
+      <c r="B118" s="2">
         <v>33950</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C118" t="s">
         <v>178</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E118" t="s">
         <v>178</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/testing-column.xlsx
+++ b/testing-column.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\leading-zeros-dates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912A5CC4-6151-4168-A3CB-9887192B9DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4239EE-3128-4D94-B46B-0B8EC68C8904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25770" yWindow="150" windowWidth="25785" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="188">
   <si>
     <t>Solved</t>
   </si>
@@ -34,7 +34,10 @@
     <t>ExpectedCheckMe</t>
   </si>
   <si>
-    <t>FormattedFullDate0</t>
+    <t>FormattedFullDate1</t>
+  </si>
+  <si>
+    <t>FormattedFullDate</t>
   </si>
   <si>
     <t>Check Me</t>
@@ -43,6 +46,27 @@
     <t>y</t>
   </si>
   <si>
+    <t>July 1, 2015 – June 30, 2016</t>
+  </si>
+  <si>
+    <t>07/01/2015 - 06/30/2016</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>1966-67;1970-1973, 1976-77</t>
+  </si>
+  <si>
+    <t>01/01/1966 - 12/31/1967</t>
+  </si>
+  <si>
+    <t>January 30, 2015 - June 15, 2015</t>
+  </si>
+  <si>
+    <t>01/30/2015 - 06/15/2015</t>
+  </si>
+  <si>
     <t>1974-75</t>
   </si>
   <si>
@@ -67,9 +91,6 @@
     <t>01/01/1971 - 12/31/1972</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>1901-1902</t>
   </si>
   <si>
@@ -94,9 +115,6 @@
     <t>Oct. Term 1963</t>
   </si>
   <si>
-    <t>n</t>
-  </si>
-  <si>
     <t>1998, 1999, 2000</t>
   </si>
   <si>
@@ -115,36 +133,42 @@
     <t>01/01/2006 - 12/31/2007</t>
   </si>
   <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Spring 2010</t>
+  </si>
+  <si>
+    <t>2012 - 2013</t>
+  </si>
+  <si>
+    <t>01/01/2012 - 12/31/2013</t>
+  </si>
+  <si>
+    <t>2014-2015-2016</t>
+  </si>
+  <si>
+    <t>01/01/2014 - 12/31/2016</t>
+  </si>
+  <si>
+    <t>2016 (Jan., Feb., March, Apr., May, June, Dec.)</t>
+  </si>
+  <si>
+    <t>01/01/2016 - 12/31/2016</t>
+  </si>
+  <si>
+    <t>01/01/2016 (Jan., Feb., March, Apr., May, June, Dec.) - 12/31/2016 (Jan., Feb., March, Apr., May, June, Dec.)</t>
+  </si>
+  <si>
+    <t>Mayo 2016</t>
+  </si>
+  <si>
+    <t>05/01/2016 - 05/31/2016</t>
+  </si>
+  <si>
     <t>p</t>
   </si>
   <si>
-    <t>Spring 2010</t>
-  </si>
-  <si>
-    <t>2012 - 2013</t>
-  </si>
-  <si>
-    <t>01/01/2012 - 12/31/2013</t>
-  </si>
-  <si>
-    <t>2014-2015-2016</t>
-  </si>
-  <si>
-    <t>01/01/2014 - 12/31/2016</t>
-  </si>
-  <si>
-    <t>2016 (Jan., Feb., March, Apr., May, June, Dec.)</t>
-  </si>
-  <si>
-    <t>01/01/2016 (Jan., Feb., March, Apr., May, June, Dec.) - 12/31/2016 (Jan., Feb., March, Apr., May, June, Dec.)</t>
-  </si>
-  <si>
-    <t>Mayo 2016</t>
-  </si>
-  <si>
-    <t>05/01/2016 - 05/31/2016</t>
-  </si>
-  <si>
     <t>Spring, Summer &amp; Fall 2017</t>
   </si>
   <si>
@@ -205,6 +229,9 @@
     <t>01/01/1990 - 01/31/1990</t>
   </si>
   <si>
+    <t>01/01/1990</t>
+  </si>
+  <si>
     <t>January 1 - January 31 1990</t>
   </si>
   <si>
@@ -557,27 +584,6 @@
   </si>
   <si>
     <t>12/12/1992</t>
-  </si>
-  <si>
-    <t>January 30, 2015 - June 15, 2015</t>
-  </si>
-  <si>
-    <t>01/30/2015 - 06/15/2015</t>
-  </si>
-  <si>
-    <t>1966-67;1970-1973, 1976-77</t>
-  </si>
-  <si>
-    <t>01/01/1966 - 12/31/1967</t>
-  </si>
-  <si>
-    <t>July 1, 2015 – June 30, 2016</t>
-  </si>
-  <si>
-    <t>07/01/2015 - 06/30/2016</t>
-  </si>
-  <si>
-    <t>01/01/2016 - 12/31/2016</t>
   </si>
 </sst>
 </file>
@@ -585,9 +591,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,11 +605,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -641,18 +642,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -955,18 +950,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="94.28515625" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.28515625" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -985,1837 +981,2276 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="E9" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="F9" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="G20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>185</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="F23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25">
         <v>40178</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="F25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" s="2">
         <v>36161</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="F26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27" s="2">
         <v>36557</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="F27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="F29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="F30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" t="s">
         <v>52</v>
       </c>
-      <c r="E31" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" t="s">
-        <v>56</v>
-      </c>
-      <c r="E34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F34" t="s">
+        <v>64</v>
+      </c>
+      <c r="G34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="F35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="F36" t="s">
+        <v>68</v>
+      </c>
+      <c r="G36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="F37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="F38" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" t="s">
+        <v>75</v>
+      </c>
+      <c r="F40" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" t="s">
+        <v>76</v>
+      </c>
+      <c r="G41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s">
+        <v>78</v>
+      </c>
+      <c r="F42" t="s">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" t="s">
+        <v>78</v>
+      </c>
+      <c r="F43" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" t="s">
+        <v>81</v>
+      </c>
+      <c r="G44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" t="s">
+        <v>81</v>
+      </c>
+      <c r="G45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" t="s">
+        <v>84</v>
+      </c>
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" t="s">
+        <v>84</v>
+      </c>
+      <c r="F46" t="s">
+        <v>84</v>
+      </c>
+      <c r="G46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" t="s">
+        <v>84</v>
+      </c>
+      <c r="F47" t="s">
+        <v>84</v>
+      </c>
+      <c r="G47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" t="s">
+        <v>87</v>
+      </c>
+      <c r="F48" t="s">
+        <v>87</v>
+      </c>
+      <c r="G48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" t="s">
+        <v>89</v>
+      </c>
+      <c r="G49" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" t="s">
+        <v>89</v>
+      </c>
+      <c r="D50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" t="s">
+        <v>89</v>
+      </c>
+      <c r="F50" t="s">
+        <v>89</v>
+      </c>
+      <c r="G50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" t="s">
+        <v>92</v>
+      </c>
+      <c r="F51" t="s">
+        <v>92</v>
+      </c>
+      <c r="G51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" t="s">
+        <v>92</v>
+      </c>
+      <c r="F52" t="s">
+        <v>92</v>
+      </c>
+      <c r="G52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>89</v>
+      </c>
+      <c r="F53" t="s">
+        <v>89</v>
+      </c>
+      <c r="G53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" t="s">
+        <v>92</v>
+      </c>
+      <c r="G54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" t="s">
+        <v>96</v>
+      </c>
+      <c r="F55" t="s">
+        <v>96</v>
+      </c>
+      <c r="G55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>97</v>
+      </c>
+      <c r="C56" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" t="s">
+        <v>98</v>
+      </c>
+      <c r="F56" t="s">
+        <v>98</v>
+      </c>
+      <c r="G56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C57" t="s">
+        <v>100</v>
+      </c>
+      <c r="E57" t="s">
+        <v>100</v>
+      </c>
+      <c r="F57" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" t="s">
+        <v>102</v>
+      </c>
+      <c r="E58" t="s">
+        <v>102</v>
+      </c>
+      <c r="F58" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>103</v>
+      </c>
+      <c r="C59" t="s">
+        <v>104</v>
+      </c>
+      <c r="E59" t="s">
+        <v>104</v>
+      </c>
+      <c r="F59" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" t="s">
+        <v>105</v>
+      </c>
+      <c r="C60" t="s">
         <v>64</v>
       </c>
-      <c r="D39" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="E60" t="s">
         <v>64</v>
       </c>
-      <c r="F39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" t="s">
-        <v>65</v>
-      </c>
-      <c r="C40" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" t="s">
-        <v>66</v>
-      </c>
-      <c r="F40" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D41" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41" t="s">
-        <v>67</v>
-      </c>
-      <c r="F41" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" t="s">
-        <v>69</v>
-      </c>
-      <c r="D42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42" t="s">
-        <v>69</v>
-      </c>
-      <c r="F42" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" t="s">
-        <v>69</v>
-      </c>
-      <c r="D43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" t="s">
-        <v>69</v>
-      </c>
-      <c r="F43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" t="s">
-        <v>71</v>
-      </c>
-      <c r="C44" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" t="s">
-        <v>72</v>
-      </c>
-      <c r="F44" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" t="s">
-        <v>73</v>
-      </c>
-      <c r="C45" t="s">
-        <v>72</v>
-      </c>
-      <c r="D45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" t="s">
-        <v>72</v>
-      </c>
-      <c r="F45" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C46" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" t="s">
-        <v>6</v>
-      </c>
-      <c r="E46" t="s">
-        <v>75</v>
-      </c>
-      <c r="F46" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" t="s">
-        <v>76</v>
-      </c>
-      <c r="C47" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" t="s">
-        <v>6</v>
-      </c>
-      <c r="E47" t="s">
-        <v>75</v>
-      </c>
-      <c r="F47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" t="s">
-        <v>78</v>
-      </c>
-      <c r="D48" t="s">
-        <v>6</v>
-      </c>
-      <c r="E48" t="s">
-        <v>78</v>
-      </c>
-      <c r="F48" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" t="s">
-        <v>79</v>
-      </c>
-      <c r="C49" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49" t="s">
-        <v>80</v>
-      </c>
-      <c r="F49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" t="s">
-        <v>80</v>
-      </c>
-      <c r="D50" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50" t="s">
-        <v>80</v>
-      </c>
-      <c r="F50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" t="s">
-        <v>83</v>
-      </c>
-      <c r="D51" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" t="s">
-        <v>83</v>
-      </c>
-      <c r="F51" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" t="s">
-        <v>82</v>
-      </c>
-      <c r="C52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D52" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52" t="s">
-        <v>83</v>
-      </c>
-      <c r="F52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>6</v>
-      </c>
-      <c r="B53" t="s">
-        <v>84</v>
-      </c>
-      <c r="C53" t="s">
-        <v>80</v>
-      </c>
-      <c r="D53" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" t="s">
-        <v>80</v>
-      </c>
-      <c r="F53" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>6</v>
-      </c>
-      <c r="B54" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" t="s">
-        <v>83</v>
-      </c>
-      <c r="D54" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54" t="s">
-        <v>83</v>
-      </c>
-      <c r="F54" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" t="s">
-        <v>86</v>
-      </c>
-      <c r="C55" t="s">
-        <v>87</v>
-      </c>
-      <c r="D55" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" t="s">
-        <v>87</v>
-      </c>
-      <c r="F55" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" t="s">
-        <v>89</v>
-      </c>
-      <c r="D56" t="s">
-        <v>6</v>
-      </c>
-      <c r="E56" t="s">
-        <v>89</v>
-      </c>
-      <c r="F56" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" t="s">
-        <v>90</v>
-      </c>
-      <c r="C57" t="s">
-        <v>91</v>
-      </c>
-      <c r="E57" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" t="s">
-        <v>92</v>
-      </c>
-      <c r="C58" t="s">
-        <v>93</v>
-      </c>
-      <c r="E58" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" t="s">
-        <v>95</v>
-      </c>
-      <c r="E59" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" t="s">
-        <v>56</v>
-      </c>
-      <c r="E60" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F60" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C61" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E61" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="F61" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E62" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="F62" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B63" s="2">
         <v>3272</v>
       </c>
       <c r="C63" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E63" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="F63" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B64" s="2">
         <v>40919</v>
       </c>
       <c r="C64" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E64" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="F64" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B65" s="2">
         <v>40960</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E65" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="F65" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C66" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D66" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="G66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D67" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E67" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F67" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="G67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C68" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D68" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E68" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F68" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="G68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C69" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D69" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E69" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F69" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="G69" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C70" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D70" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E70" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F70" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="G70" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F71" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="G71" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C72" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D72" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F72" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="G72" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B73">
         <v>1900</v>
       </c>
       <c r="C73" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E73" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="F73" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C74" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E74" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="F74" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C75" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E75" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="F75" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B76">
         <v>1980</v>
       </c>
       <c r="C76" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E76" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="F76" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B77" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C77" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E77" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="F77" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B78" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C78" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E78" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="F78" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E79" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="F79" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C80" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E80" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="F80" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E81" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="F81" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C82" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E82" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="F82" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C83" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E83" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="F83" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C84" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E84" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="F84" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E85" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="F85" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C86" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E86" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="F86" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C87" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E87" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="F87" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B88" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C88" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E88" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+      <c r="F88" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C89" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E89" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="F89" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C90" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E90" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="F90" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B91" t="s">
+        <v>150</v>
+      </c>
+      <c r="C91" t="s">
         <v>141</v>
       </c>
-      <c r="C91" t="s">
-        <v>132</v>
-      </c>
       <c r="E91" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="F91" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C92" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E92" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="F92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C93" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E93" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="F93" t="s">
+        <v>109</v>
+      </c>
+      <c r="G93" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E94" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="F94" t="s">
+        <v>110</v>
+      </c>
+      <c r="G94" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C95" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E95" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="F95" t="s">
+        <v>109</v>
+      </c>
+      <c r="G95" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C96" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E96" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="F96" t="s">
+        <v>109</v>
+      </c>
+      <c r="G96" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C97" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E97" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="F97" t="s">
+        <v>110</v>
+      </c>
+      <c r="G97" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C98" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E98" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="F98" t="s">
+        <v>110</v>
+      </c>
+      <c r="G98" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C99" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E99" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="F99" t="s">
+        <v>109</v>
+      </c>
+      <c r="G99" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C100" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E100" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="F100" t="s">
+        <v>109</v>
+      </c>
+      <c r="G100" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C101" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E101" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="F101" t="s">
+        <v>110</v>
+      </c>
+      <c r="G101" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C102" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E102" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="F102" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C103" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E103" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="F103" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C104" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E104" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="F104" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C105" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="E105" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="F105" t="s">
+        <v>165</v>
+      </c>
+      <c r="G105" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C106" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E106" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="F106" t="s">
+        <v>167</v>
+      </c>
+      <c r="G106" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C107" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E107" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="F107" t="s">
+        <v>169</v>
+      </c>
+      <c r="G107" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C108" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="E108" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="F108" t="s">
+        <v>171</v>
+      </c>
+      <c r="G108" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C109" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E109" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="F109" t="s">
+        <v>173</v>
+      </c>
+      <c r="G109" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C110" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E110" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="F110" t="s">
+        <v>175</v>
+      </c>
+      <c r="G110" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C111" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E111" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="F111" t="s">
+        <v>177</v>
+      </c>
+      <c r="G111" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C112" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E112" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+      <c r="F112" t="s">
+        <v>179</v>
+      </c>
+      <c r="G112" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C113" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E113" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="F113" t="s">
+        <v>181</v>
+      </c>
+      <c r="G113" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C114" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E114" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="F114" t="s">
+        <v>183</v>
+      </c>
+      <c r="G114" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C115" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E115" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="F115" t="s">
+        <v>177</v>
+      </c>
+      <c r="G115" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C116" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E116" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+      <c r="F116" t="s">
+        <v>179</v>
+      </c>
+      <c r="G116" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B117" s="2">
         <v>31717</v>
       </c>
       <c r="C117" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E117" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+      <c r="F117" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B118" s="2">
         <v>33950</v>
       </c>
       <c r="C118" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E118" t="s">
-        <v>178</v>
+        <v>187</v>
+      </c>
+      <c r="F118" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/testing-column.xlsx
+++ b/testing-column.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\leading-zeros-dates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4239EE-3128-4D94-B46B-0B8EC68C8904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D01763A-87DE-45A7-9ED1-22BF114E0286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25770" yWindow="150" windowWidth="25785" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>Solved</t>
   </si>
   <si>
-    <t>FullDate</t>
+    <t>Convert Us</t>
   </si>
   <si>
     <t>Expected Result</t>
@@ -37,10 +37,10 @@
     <t>FormattedFullDate1</t>
   </si>
   <si>
-    <t>FormattedFullDate</t>
-  </si>
-  <si>
-    <t>Check Me</t>
+    <t>FormattedFullDate2</t>
+  </si>
+  <si>
+    <t>Check Me1</t>
   </si>
   <si>
     <t>y</t>
@@ -953,13 +953,12 @@
   <dimension ref="A1:G118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.28515625" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
